--- a/results/components/gene_names/p2s11.xlsx
+++ b/results/components/gene_names/p2s11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>gene1</t>
   </si>
@@ -22,34 +22,31 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>CG13850</t>
-  </si>
-  <si>
-    <t>Rho1</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
+    <t>bon</t>
+  </si>
+  <si>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
   </si>
 </sst>
 </file>
@@ -418,18 +415,18 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/results/components/gene_names/p2s11.xlsx
+++ b/results/components/gene_names/p2s11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>gene1</t>
   </si>
@@ -22,31 +22,40 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>esc</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>gl</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
+    <t>jumu</t>
+  </si>
+  <si>
+    <t>tok</t>
+  </si>
+  <si>
+    <t>Crk</t>
+  </si>
+  <si>
+    <t>RpL30</t>
+  </si>
+  <si>
+    <t>CG12301</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>brm</t>
+  </si>
+  <si>
+    <t>CG2681</t>
+  </si>
+  <si>
+    <t>Nrt</t>
+  </si>
+  <si>
+    <t>Akt1</t>
+  </si>
+  <si>
+    <t>Atpalpha</t>
+  </si>
+  <si>
+    <t>baz</t>
   </si>
 </sst>
 </file>
@@ -378,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -415,18 +424,26 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
